--- a/db/WJ_ISA.xlsx
+++ b/db/WJ_ISA.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="ROI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Portfolio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Portfolio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Balance" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,37 +472,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>연도</t>
+          <t>종목코드</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>종목명</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>투자원금</t>
+          <t>자산군</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>추가납입</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>잔고</t>
+          <t>세팅비중</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>수익률</t>
+          <t>현재비중</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>녹색매수</t>
         </is>
       </c>
     </row>
@@ -517,43 +517,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>종목코드</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>종목명</t>
+          <t>투자원금</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>자산군</t>
+          <t>추가납입</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>잔고</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>세팅비중</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>현재비중</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>녹색매수</t>
+          <t>수익률</t>
         </is>
       </c>
     </row>
